--- a/bakup/customers/mohammad hosein.xlsx
+++ b/bakup/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -808,6 +808,15 @@
   </si>
   <si>
     <t>1405/05/23</t>
+  </si>
+  <si>
+    <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1357,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4692,7 +4701,7 @@
         <v>188</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -4712,27 +4721,39 @@
     <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
-        <v>5379000</v>
-      </c>
-      <c r="B241" s="8"/>
+        <v>5450000</v>
+      </c>
+      <c r="B241" s="8">
+        <v>71000</v>
+      </c>
       <c r="C241" s="8"/>
-      <c r="D241" s="8"/>
-      <c r="E241" s="1"/>
+      <c r="D241" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
-      </c>
-      <c r="B242" s="8"/>
+        <v>5639000</v>
+      </c>
+      <c r="B242" s="8">
+        <v>189000</v>
+      </c>
       <c r="C242" s="8"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="1"/>
+      <c r="D242" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4742,7 +4763,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4752,7 +4773,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4762,7 +4783,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4772,7 +4793,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4782,7 +4803,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4792,7 +4813,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4802,7 +4823,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4812,7 +4833,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4822,7 +4843,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4832,7 +4853,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4842,7 +4863,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4852,7 +4873,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4862,7 +4883,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4872,7 +4893,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4882,7 +4903,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4893,7 +4914,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>192000</v>
+        <v>452000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4911,7 +4932,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>
